--- a/scripts_data_misc/ARG_SwingWeighting.xlsx
+++ b/scripts_data_misc/ARG_SwingWeighting.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\American River Group\2025-09-30 - Swing Weighting and MCDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/avaisvil_usbr_gov/Documents/Documents/R/american_river_SDM/scripts_data_misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE649D8-8022-46BB-B9FD-DB1D00C0BC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6FE649D8-8022-46BB-B9FD-DB1D00C0BC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7888CCD8-9C1A-4E2C-8419-EC4634312C0D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5BADBCA-A86E-465C-8AFB-FD48819B4B4A}"/>
+    <workbookView xWindow="-21600" yWindow="165" windowWidth="21600" windowHeight="11835" xr2:uid="{C5BADBCA-A86E-465C-8AFB-FD48819B4B4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -929,7 +929,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="22" t="e">
-        <f t="shared" si="0"/>
+        <f>G8/SUM($G$8:$I$8)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H9" s="22" t="e">
